--- a/data/trans_dic/P33B_R5-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R5-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,51</t>
+          <t>5,0; 8,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,94; 15,84</t>
+          <t>12,18; 16,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 11,6</t>
+          <t>9,07; 11,75</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,53</t>
+          <t>4,63; 7,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,42</t>
+          <t>11,16; 14,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,69</t>
+          <t>8,16; 10,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,96</t>
+          <t>4,39; 7,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 11,89</t>
+          <t>9,48; 13,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 9,24</t>
+          <t>7,48; 10,18</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,38</t>
+          <t>6,96; 10,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 14,51</t>
+          <t>11,34; 14,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 11,91</t>
+          <t>9,7; 12,06</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,33</t>
+          <t>5,9; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 12,91</t>
+          <t>11,83; 13,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,91</t>
+          <t>9,2; 10,42</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>45782</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92177</t>
+          <t>102199</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133703</t>
+          <t>147981</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31041; 54013</t>
+          <t>34476; 58934</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80668; 106972</t>
+          <t>89250; 118918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118231; 151931</t>
+          <t>128998; 167138</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>55109</t>
+          <t>61337</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>121751</t>
+          <t>135870</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176860</t>
+          <t>197207</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27848; 77880</t>
+          <t>48606; 78795</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>105903; 138150</t>
+          <t>119521; 153945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>116171; 208513</t>
+          <t>172972; 221385</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80106</t>
+          <t>92374</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123152</t>
+          <t>139822</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31989; 56047</t>
+          <t>35200; 61705</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38055; 110865</t>
+          <t>76849; 111342</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80576; 151181</t>
+          <t>120643; 164273</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>79235</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>133597</t>
+          <t>143792</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212832</t>
+          <t>226802</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64793; 96178</t>
+          <t>68887; 103934</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>108743; 158509</t>
+          <t>126853; 164628</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181355; 240433</t>
+          <t>204512; 254188</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>427630</t>
+          <t>474236</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>646547</t>
+          <t>711812</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>168381; 253439</t>
+          <t>208439; 268293</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>348865; 472318</t>
+          <t>441591; 507802</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557091; 705134</t>
+          <t>668340; 756581</t>
         </is>
       </c>
     </row>
